--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -723,60 +723,64 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +794,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -800,33 +804,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>2/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +842,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +852,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,43 +913,947 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>—/3</t>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -753,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -780,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -872,19 +880,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -899,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -991,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1018,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -1100,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1133,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1157,33 +1169,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1244,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1405,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1510,13 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1627,7 +1655,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1738,7 +1766,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1746,22 +1774,22 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1794,12 +1822,12 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1848,12 +1876,805 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,17 +1518,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1534,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1655,7 +1659,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1766,7 +1770,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1881,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1996,7 +2000,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2107,7 +2111,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2222,7 +2226,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2333,7 +2337,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2398,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2448,7 +2452,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2513,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2558,12 +2562,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2628,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2674,7 +2678,229 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1576,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1633,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1687,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -1720,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1798,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1831,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1855,17 +1875,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1875,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1913,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1946,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1970,32 +1994,32 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2061,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2100,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2172,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2287,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2513,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2567,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2904,6 +2928,688 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1824,24 +1824,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,17 +2113,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2129,13 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2250,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2278,32 +2286,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -2311,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2335,33 +2347,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2389,32 +2405,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2422,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2446,17 +2466,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2466,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2504,32 +2524,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2537,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2561,37 +2585,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2619,32 +2643,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2652,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2676,33 +2704,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2730,32 +2762,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2763,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2787,33 +2823,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2841,32 +2881,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2874,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2898,33 +2942,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3024,7 +3072,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3096,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3150,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3265,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3495,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3503,22 +3551,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3551,12 +3599,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3570,41 +3618,846 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr"/>
-      <c r="AC27" s="2" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>—/14</t>
         </is>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,13 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2377,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2723,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2734,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2891,24 +2895,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2918,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,7 +2971,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3000,32 +3004,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3033,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3057,17 +3065,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3077,13 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3111,32 +3123,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3144,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,37 +3184,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3226,32 +3242,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3259,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,17 +3303,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3303,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3341,32 +3361,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3374,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,32 +3422,32 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3456,32 +3480,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -3489,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,37 +3541,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3571,32 +3599,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3604,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3628,17 +3660,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3648,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3686,32 +3718,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -3719,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3743,37 +3779,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3873,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3888,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4003,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,7 +4139,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4118,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4228,7 +4264,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4294,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4356,22 +4392,22 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4404,12 +4440,12 @@
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4423,43 +4459,737 @@
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>11:25</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
-      <c r="AC34" s="2" t="inlineStr">
-        <is>
-          <t>—/14</t>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3728,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3837,32 +3837,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -3870,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3898,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3914,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3952,32 +3956,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3985,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4017,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4029,17 +4037,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4067,32 +4075,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -4100,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,17 +4136,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4144,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4182,32 +4194,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4215,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,37 +4255,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4297,32 +4313,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4330,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4354,37 +4374,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4412,32 +4432,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4445,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4469,17 +4493,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4489,17 +4513,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,7 +4623,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4614,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4642,32 +4666,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -4675,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4699,17 +4727,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4719,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4839,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4944,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4959,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5064,17 +5092,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5179,17 +5207,703 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>4/14</t>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,22 +3913,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4551,32 +4551,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4584,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4608,17 +4612,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4628,17 +4632,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4676,24 +4680,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4703,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4752,12 +4756,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4785,32 +4789,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -4818,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,17 +4850,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4862,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4900,32 +4908,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4933,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4957,17 +4969,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4977,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5015,32 +5027,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5048,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5072,17 +5088,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5092,17 +5108,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5130,32 +5146,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -5163,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,37 +5207,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5332,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5432,7 +5452,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5447,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5662,7 +5682,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5734,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5907,6 +5927,577 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,14 +1775,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,14 +3556,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,22 +4627,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,14 +4746,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5156,24 +5156,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5326,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5342,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5380,32 +5384,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5413,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5437,17 +5445,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5457,12 +5465,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5495,32 +5503,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5528,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,37 +5564,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5610,32 +5622,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -5643,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,17 +5683,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5687,13 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5741,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5754,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,32 +5802,32 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5869,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5908,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5923,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5984,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6033,12 +6057,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6138,7 +6162,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6214,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,12 +6282,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6329,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6444,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,13 +6512,592 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>76.7</t>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>76.7</t>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>76.7</t>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5860,32 +5860,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5921,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5937,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5975,32 +5979,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -6008,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6032,17 +6040,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6052,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6090,32 +6098,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6123,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6159,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6167,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6217,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6238,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,17 +6278,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6282,12 +6298,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6353,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6392,7 +6408,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6468,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6583,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6698,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6813,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6857,17 +6873,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6990,22 +7006,22 @@
       <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7038,12 +7054,12 @@
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7057,47 +7073,392 @@
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W56" s="2" t="inlineStr">
+      <c r="W57" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X56" s="2" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y56" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z56" s="2" t="inlineStr">
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>10/15</t>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,17 +1775,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,14 +2604,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,14 +4032,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,17 +4746,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6108,19 +6108,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6336,32 +6336,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6369,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,17 +6397,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6413,17 +6417,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6451,32 +6455,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -6484,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6508,17 +6516,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6528,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6566,32 +6574,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6599,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,32 +6635,32 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6714,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6829,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7059,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7113,7 +7125,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7223,12 +7235,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7351,22 +7363,22 @@
       <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7399,12 +7411,12 @@
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7443,22 +7455,367 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,22 +4627,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,22 +4865,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,22 +5579,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,17 +5817,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,22 +5936,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6584,24 +6584,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6693,32 +6693,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6726,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,37 +6754,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6808,32 +6812,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6841,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6865,37 +6873,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6923,32 +6931,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6956,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6980,32 +6992,32 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7038,32 +7050,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -7071,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7095,37 +7111,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7153,32 +7169,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7186,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7210,17 +7230,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7230,12 +7250,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7301,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7360,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7416,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7531,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7646,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7700,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7810,12 +7830,1047 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
           <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,17 +1775,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,22 +2604,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,22 +3318,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,22 +3913,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,22 +4032,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,17 +4627,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,17 +4746,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,17 +5108,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,22 +5222,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,17 +5579,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,22 +6412,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6650,17 +6650,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6769,17 +6769,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7060,24 +7060,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7179,24 +7179,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7288,32 +7288,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7321,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,17 +7349,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7365,17 +7369,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7403,32 +7407,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -7436,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,37 +7468,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7518,32 +7526,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7551,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7575,37 +7587,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7633,32 +7645,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7666,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7690,37 +7706,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7748,32 +7764,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -7781,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7805,32 +7825,32 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7863,32 +7883,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -7896,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,27 +7944,27 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -8011,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8065,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8093,32 +8117,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8126,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8150,32 +8178,32 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8241,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8356,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8471,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8525,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8635,7 +8663,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8701,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8816,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8860,17 +8888,822 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
           <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>81.4</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,17 +2132,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,22 +3675,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,17 +3794,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,22 +3913,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,22 +4389,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,22 +4508,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,17 +5103,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,22 +5222,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,22 +5341,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,17 +5817,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,22 +5936,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,22 +6174,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6531,22 +6531,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6888,22 +6888,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7007,17 +7007,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7126,17 +7126,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7245,22 +7245,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,22 +7483,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8002,32 +8002,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -8035,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,37 +8063,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8127,24 +8131,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8154,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8203,7 +8207,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8236,32 +8240,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -8269,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,37 +8301,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8359,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8384,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,32 +8420,32 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8466,32 +8478,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8499,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,37 +8539,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8581,32 +8597,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -8614,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8638,32 +8658,32 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8696,32 +8716,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8729,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8753,37 +8777,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8811,32 +8835,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -8844,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,32 +8896,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8926,32 +8954,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -8959,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8983,37 +9015,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9041,32 +9073,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9074,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9098,37 +9134,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9304,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9343,7 +9379,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9419,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9481,22 +9517,22 @@
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9529,12 +9565,12 @@
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9548,7 +9584,7 @@
       <c r="T77" s="2" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
@@ -9573,22 +9609,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9632,7 @@
       <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -9606,7 +9642,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -9644,12 +9680,12 @@
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9663,47 +9699,1197 @@
       <c r="T78" s="2" t="inlineStr"/>
       <c r="U78" s="2" t="inlineStr">
         <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>81.4</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="V78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W78" s="2" t="inlineStr">
+      <c r="W80" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X78" s="2" t="inlineStr">
+      <c r="X80" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y78" s="2" t="inlineStr">
+      <c r="Y80" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z78" s="2" t="inlineStr">
+      <c r="Z80" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB78" s="2" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr">
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
         <is>
           <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC88"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,22 +4389,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,22 +4508,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,22 +4746,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,22 +5341,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,17 +5460,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6650,22 +6650,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7840,22 +7840,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7959,17 +7959,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8078,22 +8078,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8321,17 +8321,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8554,22 +8554,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9307,32 +9307,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9340,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9364,17 +9368,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9384,12 +9388,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9422,32 +9426,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9455,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,32 +9487,32 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9537,32 +9545,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9570,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,37 +9606,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9652,32 +9664,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -9685,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9709,37 +9725,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9767,32 +9783,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -9800,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9824,17 +9844,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9844,17 +9864,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9882,32 +9902,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9915,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9939,17 +9963,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9959,12 +9983,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10030,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10112,32 +10136,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10145,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10169,37 +10197,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10299,7 +10327,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10375,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10429,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10529,7 +10557,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10544,7 +10572,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10720,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10782,22 +10810,22 @@
       <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -10830,12 +10858,12 @@
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10884,12 +10912,817 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
           <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,17 +5108,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6417,17 +6417,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6893,17 +6893,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7369,17 +7369,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7607,17 +7607,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7726,17 +7726,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8797,17 +8797,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8916,17 +8916,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9154,12 +9154,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,17 +9269,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,17 +9388,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10370,32 +10370,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10403,7 +10407,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10427,17 +10431,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10447,17 +10451,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10485,32 +10489,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -10518,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10542,17 +10550,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10562,17 +10570,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10600,32 +10608,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10633,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10657,17 +10669,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10677,12 +10689,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10748,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10830,32 +10842,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10863,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10887,17 +10903,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10907,17 +10923,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10945,32 +10961,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10978,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11002,17 +11022,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11022,17 +11042,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11175,32 +11195,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11208,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11232,17 +11256,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11252,12 +11276,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11323,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11438,7 +11462,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11477,7 +11501,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11500,22 +11524,22 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11548,12 +11572,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11567,7 +11591,7 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
@@ -11592,22 +11616,22 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -11615,7 +11639,7 @@
       <c r="A95" s="2" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -11625,7 +11649,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -11663,12 +11687,12 @@
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11682,47 +11706,392 @@
       <c r="T95" s="2" t="inlineStr"/>
       <c r="U95" s="2" t="inlineStr">
         <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z95" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
-        <is>
-          <t>78.4</t>
-        </is>
-      </c>
-      <c r="AC95" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7131,17 +7131,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7964,17 +7964,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8083,17 +8083,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8321,17 +8321,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8678,17 +8678,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9507,17 +9507,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9626,17 +9626,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9864,17 +9864,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10332,17 +10332,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11080,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11113,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11137,17 +11141,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11157,17 +11161,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11205,24 +11209,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11232,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11281,7 +11285,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11429,32 +11433,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11462,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11486,17 +11494,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11506,17 +11514,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -11544,32 +11552,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -11577,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11601,17 +11613,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11621,17 +11633,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -11659,32 +11671,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -11692,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11716,17 +11732,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11736,17 +11752,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11774,32 +11790,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -11807,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11831,17 +11851,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11851,7 +11871,7 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
@@ -11861,7 +11881,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11966,17 +11986,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12057,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12081,17 +12101,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-浦东78路.xlsx
+++ b/data/export/2026-10-05-浦东78路.xlsx
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11514,12 +11514,12 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11909,32 +11909,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11942,7 +11946,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11966,17 +11970,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11986,12 +11990,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12057,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
